--- a/backend/upload/sp_2015_kyokwa_subject.xlsx
+++ b/backend/upload/sp_2015_kyokwa_subject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\github\StudyPlanner\backend\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3882B4A7-41E0-4A28-BF73-1323EA99E0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF6EB79-CF70-45F0-8A92-65DF18BFD7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25135CD0-B9EC-4BE9-87A7-1D0FB89CCED0}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{25135CD0-B9EC-4BE9-87A7-1D0FB89CCED0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="525">
   <si>
     <t>ID</t>
   </si>
@@ -1596,6 +1596,26 @@
   </si>
   <si>
     <t>음악사</t>
+  </si>
+  <si>
+    <t>수능국어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능수학</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>표점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수능영어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1979,7 +1999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8EB1B9-E17F-4729-B1DD-5BBFAB508EEB}">
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -2009,8 +2029,9 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>8</v>
+      <c r="A2" t="str">
+        <f>C2&amp;E2&amp;G2</f>
+        <v>15H0100</v>
       </c>
       <c r="B2" t="s">
         <v>9</v>
@@ -2019,24 +2040,24 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>521</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>520</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -2045,13 +2066,13 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2062,7 +2083,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
@@ -2077,10 +2098,10 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>12</v>
@@ -2088,7 +2109,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -2103,10 +2124,10 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
@@ -2114,7 +2135,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
@@ -2129,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H6" t="s">
         <v>12</v>
@@ -2140,7 +2161,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -2149,24 +2170,24 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -2181,10 +2202,10 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
         <v>25</v>
@@ -2192,7 +2213,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -2207,10 +2228,10 @@
         <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
         <v>25</v>
@@ -2218,33 +2239,34 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>33</v>
+      <c r="A11" t="str">
+        <f>C11&amp;E11&amp;G11</f>
+        <v>15H0200</v>
       </c>
       <c r="B11" t="s">
         <v>31</v>
@@ -2253,24 +2275,24 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>521</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>522</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
@@ -2279,16 +2301,16 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>12</v>
@@ -2296,7 +2318,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
@@ -2311,10 +2333,10 @@
         <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>12</v>
@@ -2322,7 +2344,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -2337,10 +2359,10 @@
         <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H14" t="s">
         <v>12</v>
@@ -2348,7 +2370,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
         <v>31</v>
@@ -2357,24 +2379,24 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -2383,24 +2405,24 @@
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>31</v>
@@ -2415,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>25</v>
@@ -2426,7 +2448,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
@@ -2441,10 +2463,10 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" t="s">
         <v>25</v>
@@ -2452,7 +2474,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
@@ -2467,10 +2489,10 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H19" t="s">
         <v>25</v>
@@ -2478,7 +2500,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>31</v>
@@ -2493,10 +2515,10 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20" t="s">
         <v>25</v>
@@ -2504,7 +2526,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>31</v>
@@ -2519,10 +2541,10 @@
         <v>3</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H21" t="s">
         <v>25</v>
@@ -2530,7 +2552,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
         <v>31</v>
@@ -2545,10 +2567,10 @@
         <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H22" t="s">
         <v>25</v>
@@ -2556,7 +2578,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
         <v>31</v>
@@ -2571,10 +2593,10 @@
         <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" t="s">
         <v>25</v>
@@ -2582,7 +2604,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B24" t="s">
         <v>31</v>
@@ -2597,10 +2619,10 @@
         <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H24" t="s">
         <v>25</v>
@@ -2608,59 +2630,60 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>66</v>
+      <c r="A27" t="str">
+        <f>C27&amp;E27&amp;G27</f>
+        <v>15H0300</v>
       </c>
       <c r="B27" t="s">
         <v>62</v>
@@ -2669,24 +2692,24 @@
         <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>521</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>67</v>
+        <v>524</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>523</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
         <v>62</v>
@@ -2695,16 +2718,16 @@
         <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -2712,7 +2735,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>62</v>
@@ -2727,10 +2750,10 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -2738,7 +2761,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
         <v>62</v>
@@ -2747,24 +2770,24 @@
         <v>63</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
@@ -2773,24 +2796,24 @@
         <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>62</v>
@@ -2799,24 +2822,24 @@
         <v>63</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
         <v>62</v>
@@ -2831,10 +2854,10 @@
         <v>3</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
         <v>25</v>
@@ -2842,7 +2865,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B34" t="s">
         <v>62</v>
@@ -2857,10 +2880,10 @@
         <v>3</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H34" t="s">
         <v>25</v>
@@ -2868,7 +2891,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B35" t="s">
         <v>62</v>
@@ -2883,10 +2906,10 @@
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G35">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H35" t="s">
         <v>25</v>
@@ -2894,7 +2917,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B36" t="s">
         <v>62</v>
@@ -2909,10 +2932,10 @@
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H36" t="s">
         <v>25</v>
@@ -2920,7 +2943,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B37" t="s">
         <v>62</v>
@@ -2935,10 +2958,10 @@
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H37" t="s">
         <v>25</v>
@@ -2946,7 +2969,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B38" t="s">
         <v>62</v>
@@ -2961,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="G38">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H38" t="s">
         <v>25</v>
@@ -2972,7 +2995,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B39" t="s">
         <v>62</v>
@@ -2987,10 +3010,10 @@
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G39">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H39" t="s">
         <v>25</v>
@@ -2998,7 +3021,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B40" t="s">
         <v>62</v>
@@ -3013,10 +3036,10 @@
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G40">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H40" t="s">
         <v>25</v>
@@ -3024,7 +3047,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B41" t="s">
         <v>62</v>
@@ -3039,10 +3062,10 @@
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="G41">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H41" t="s">
         <v>25</v>
@@ -3050,7 +3073,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
@@ -3065,10 +3088,10 @@
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G42">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H42" t="s">
         <v>25</v>
@@ -3076,85 +3099,85 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
+        <v>93</v>
+      </c>
+      <c r="G43">
         <v>11</v>
       </c>
-      <c r="E43">
-        <v>1</v>
-      </c>
-      <c r="F43" t="s">
-        <v>101</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
       <c r="H43" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B45" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B46" t="s">
         <v>99</v>
@@ -3163,16 +3186,16 @@
         <v>100</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
         <v>12</v>
@@ -3180,7 +3203,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B47" t="s">
         <v>99</v>
@@ -3195,10 +3218,10 @@
         <v>2</v>
       </c>
       <c r="F47" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
@@ -3206,7 +3229,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
         <v>99</v>
@@ -3221,10 +3244,10 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H48" t="s">
         <v>12</v>
@@ -3232,7 +3255,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B49" t="s">
         <v>99</v>
@@ -3247,10 +3270,10 @@
         <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="G49">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
@@ -3258,7 +3281,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
         <v>99</v>
@@ -3273,10 +3296,10 @@
         <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G50">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H50" t="s">
         <v>12</v>
@@ -3284,7 +3307,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B51" t="s">
         <v>99</v>
@@ -3299,10 +3322,10 @@
         <v>2</v>
       </c>
       <c r="F51" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G51">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H51" t="s">
         <v>12</v>
@@ -3310,7 +3333,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B52" t="s">
         <v>99</v>
@@ -3325,10 +3348,10 @@
         <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G52">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H52" t="s">
         <v>12</v>
@@ -3336,7 +3359,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
         <v>99</v>
@@ -3345,24 +3368,24 @@
         <v>100</v>
       </c>
       <c r="D53" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H53" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B54" t="s">
         <v>99</v>
@@ -3371,24 +3394,24 @@
         <v>100</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H54" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B55" t="s">
         <v>99</v>
@@ -3397,24 +3420,24 @@
         <v>100</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B56" t="s">
         <v>99</v>
@@ -3429,10 +3452,10 @@
         <v>3</v>
       </c>
       <c r="F56" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H56" t="s">
         <v>25</v>
@@ -3440,7 +3463,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
         <v>99</v>
@@ -3455,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H57" t="s">
         <v>25</v>
@@ -3466,7 +3489,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B58" t="s">
         <v>99</v>
@@ -3481,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="F58" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="G58">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H58" t="s">
         <v>25</v>
@@ -3492,7 +3515,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B59" t="s">
         <v>99</v>
@@ -3507,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="F59" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G59">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H59" t="s">
         <v>25</v>
@@ -3518,7 +3541,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B60" t="s">
         <v>99</v>
@@ -3533,10 +3556,10 @@
         <v>3</v>
       </c>
       <c r="F60" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H60" t="s">
         <v>25</v>
@@ -3544,7 +3567,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B61" t="s">
         <v>99</v>
@@ -3559,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="F61" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G61">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H61" t="s">
         <v>25</v>
@@ -3570,7 +3593,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B62" t="s">
         <v>99</v>
@@ -3585,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G62">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H62" t="s">
         <v>25</v>
@@ -3596,7 +3619,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B63" t="s">
         <v>99</v>
@@ -3611,10 +3634,10 @@
         <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G63">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H63" t="s">
         <v>25</v>
@@ -3622,7 +3645,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B64" t="s">
         <v>99</v>
@@ -3637,10 +3660,10 @@
         <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G64">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H64" t="s">
         <v>25</v>
@@ -3648,7 +3671,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B65" t="s">
         <v>99</v>
@@ -3663,10 +3686,10 @@
         <v>3</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G65">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H65" t="s">
         <v>25</v>
@@ -3674,7 +3697,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
         <v>99</v>
@@ -3689,10 +3712,10 @@
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G66">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H66" t="s">
         <v>25</v>
@@ -3700,25 +3723,25 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H67" t="s">
         <v>25</v>
@@ -3726,59 +3749,59 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H68" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69" t="s">
+        <v>147</v>
+      </c>
+      <c r="G69">
         <v>14</v>
       </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="F69" t="s">
-        <v>155</v>
-      </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
       <c r="H69" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
         <v>149</v>
@@ -3787,24 +3810,24 @@
         <v>150</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
         <v>149</v>
@@ -3813,16 +3836,16 @@
         <v>150</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71" t="s">
+        <v>153</v>
+      </c>
+      <c r="G71">
         <v>2</v>
-      </c>
-      <c r="F71" t="s">
-        <v>159</v>
-      </c>
-      <c r="G71">
-        <v>3</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -3830,7 +3853,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B72" t="s">
         <v>149</v>
@@ -3845,10 +3868,10 @@
         <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="G72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -3856,7 +3879,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B73" t="s">
         <v>149</v>
@@ -3865,24 +3888,24 @@
         <v>150</v>
       </c>
       <c r="D73" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B74" t="s">
         <v>149</v>
@@ -3891,24 +3914,24 @@
         <v>150</v>
       </c>
       <c r="D74" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B75" t="s">
         <v>149</v>
@@ -3917,24 +3940,24 @@
         <v>150</v>
       </c>
       <c r="D75" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B76" t="s">
         <v>149</v>
@@ -3949,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" t="s">
         <v>25</v>
@@ -3960,7 +3983,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B77" t="s">
         <v>149</v>
@@ -3975,10 +3998,10 @@
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H77" t="s">
         <v>25</v>
@@ -3986,7 +4009,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B78" t="s">
         <v>149</v>
@@ -4001,10 +4024,10 @@
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G78">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H78" t="s">
         <v>25</v>
@@ -4012,7 +4035,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B79" t="s">
         <v>149</v>
@@ -4027,10 +4050,10 @@
         <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G79">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H79" t="s">
         <v>25</v>
@@ -4038,7 +4061,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
         <v>149</v>
@@ -4053,10 +4076,10 @@
         <v>3</v>
       </c>
       <c r="F80" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H80" t="s">
         <v>25</v>
@@ -4064,7 +4087,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B81" t="s">
         <v>149</v>
@@ -4079,10 +4102,10 @@
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G81">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H81" t="s">
         <v>25</v>
@@ -4090,7 +4113,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B82" t="s">
         <v>149</v>
@@ -4105,10 +4128,10 @@
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="G82">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H82" t="s">
         <v>25</v>
@@ -4116,7 +4139,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B83" t="s">
         <v>149</v>
@@ -4131,10 +4154,10 @@
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G83">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H83" t="s">
         <v>25</v>
@@ -4142,7 +4165,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B84" t="s">
         <v>149</v>
@@ -4157,10 +4180,10 @@
         <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G84">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H84" t="s">
         <v>25</v>
@@ -4168,7 +4191,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B85" t="s">
         <v>149</v>
@@ -4183,10 +4206,10 @@
         <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G85">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H85" t="s">
         <v>25</v>
@@ -4194,7 +4217,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B86" t="s">
         <v>149</v>
@@ -4209,10 +4232,10 @@
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G86">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H86" t="s">
         <v>25</v>
@@ -4220,7 +4243,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B87" t="s">
         <v>149</v>
@@ -4235,10 +4258,10 @@
         <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="G87">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H87" t="s">
         <v>25</v>
@@ -4246,7 +4269,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B88" t="s">
         <v>149</v>
@@ -4261,10 +4284,10 @@
         <v>3</v>
       </c>
       <c r="F88" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G88">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H88" t="s">
         <v>25</v>
@@ -4272,7 +4295,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B89" t="s">
         <v>149</v>
@@ -4287,10 +4310,10 @@
         <v>3</v>
       </c>
       <c r="F89" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="G89">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H89" t="s">
         <v>25</v>
@@ -4298,7 +4321,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B90" t="s">
         <v>149</v>
@@ -4313,10 +4336,10 @@
         <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="G90">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H90" t="s">
         <v>25</v>
@@ -4324,7 +4347,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B91" t="s">
         <v>149</v>
@@ -4339,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="G91">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
         <v>25</v>
@@ -4350,85 +4373,85 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B92" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="C92" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="D92" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G92">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G93">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H93" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>150</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F94" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H94" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B95" t="s">
         <v>201</v>
@@ -4443,10 +4466,10 @@
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G95">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
         <v>12</v>
@@ -4454,7 +4477,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
         <v>201</v>
@@ -4469,10 +4492,10 @@
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -4480,7 +4503,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B97" t="s">
         <v>201</v>
@@ -4495,10 +4518,10 @@
         <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="G97">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -4506,7 +4529,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B98" t="s">
         <v>201</v>
@@ -4521,10 +4544,10 @@
         <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G98">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H98" t="s">
         <v>12</v>
@@ -4532,7 +4555,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
         <v>201</v>
@@ -4547,10 +4570,10 @@
         <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G99">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -4558,7 +4581,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
         <v>201</v>
@@ -4573,10 +4596,10 @@
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="G100">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -4584,7 +4607,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
         <v>201</v>
@@ -4599,10 +4622,10 @@
         <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="G101">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -4610,7 +4633,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
         <v>201</v>
@@ -4625,10 +4648,10 @@
         <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G102">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H102" t="s">
         <v>12</v>
@@ -4636,7 +4659,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
         <v>201</v>
@@ -4651,10 +4674,10 @@
         <v>2</v>
       </c>
       <c r="F103" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G103">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H103" t="s">
         <v>12</v>
@@ -4662,7 +4685,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
         <v>201</v>
@@ -4677,10 +4700,10 @@
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G104">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H104" t="s">
         <v>12</v>
@@ -4688,7 +4711,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
         <v>201</v>
@@ -4703,10 +4726,10 @@
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G105">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H105" t="s">
         <v>12</v>
@@ -4714,7 +4737,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
         <v>201</v>
@@ -4729,10 +4752,10 @@
         <v>2</v>
       </c>
       <c r="F106" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G106">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H106" t="s">
         <v>12</v>
@@ -4740,7 +4763,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B107" t="s">
         <v>201</v>
@@ -4755,10 +4778,10 @@
         <v>2</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G107">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H107" t="s">
         <v>12</v>
@@ -4766,7 +4789,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s">
         <v>201</v>
@@ -4781,10 +4804,10 @@
         <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="G108">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H108" t="s">
         <v>12</v>
@@ -4792,7 +4815,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B109" t="s">
         <v>201</v>
@@ -4807,10 +4830,10 @@
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G109">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H109" t="s">
         <v>12</v>
@@ -4818,7 +4841,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B110" t="s">
         <v>201</v>
@@ -4833,10 +4856,10 @@
         <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G110">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
         <v>12</v>
@@ -4844,7 +4867,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B111" t="s">
         <v>201</v>
@@ -4859,10 +4882,10 @@
         <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="G111">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -4870,7 +4893,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B112" t="s">
         <v>201</v>
@@ -4885,10 +4908,10 @@
         <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="G112">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H112" t="s">
         <v>12</v>
@@ -4896,7 +4919,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B113" t="s">
         <v>201</v>
@@ -4905,24 +4928,24 @@
         <v>202</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="G113">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H113" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
         <v>201</v>
@@ -4931,24 +4954,24 @@
         <v>202</v>
       </c>
       <c r="D114" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="G114">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B115" t="s">
         <v>201</v>
@@ -4957,24 +4980,24 @@
         <v>202</v>
       </c>
       <c r="D115" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F115" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G115">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="H115" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B116" t="s">
         <v>201</v>
@@ -4989,10 +5012,10 @@
         <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H116" t="s">
         <v>25</v>
@@ -5000,7 +5023,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B117" t="s">
         <v>201</v>
@@ -5015,10 +5038,10 @@
         <v>3</v>
       </c>
       <c r="F117" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H117" t="s">
         <v>25</v>
@@ -5026,7 +5049,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B118" t="s">
         <v>201</v>
@@ -5041,10 +5064,10 @@
         <v>3</v>
       </c>
       <c r="F118" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H118" t="s">
         <v>25</v>
@@ -5052,7 +5075,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B119" t="s">
         <v>201</v>
@@ -5067,10 +5090,10 @@
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H119" t="s">
         <v>25</v>
@@ -5078,7 +5101,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B120" t="s">
         <v>201</v>
@@ -5093,10 +5116,10 @@
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="G120">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H120" t="s">
         <v>25</v>
@@ -5104,7 +5127,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B121" t="s">
         <v>201</v>
@@ -5119,10 +5142,10 @@
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="G121">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H121" t="s">
         <v>25</v>
@@ -5130,7 +5153,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B122" t="s">
         <v>201</v>
@@ -5145,10 +5168,10 @@
         <v>3</v>
       </c>
       <c r="F122" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G122">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H122" t="s">
         <v>25</v>
@@ -5156,7 +5179,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B123" t="s">
         <v>201</v>
@@ -5171,10 +5194,10 @@
         <v>3</v>
       </c>
       <c r="F123" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G123">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H123" t="s">
         <v>25</v>
@@ -5182,7 +5205,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B124" t="s">
         <v>201</v>
@@ -5197,10 +5220,10 @@
         <v>3</v>
       </c>
       <c r="F124" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G124">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H124" t="s">
         <v>25</v>
@@ -5208,7 +5231,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B125" t="s">
         <v>201</v>
@@ -5223,10 +5246,10 @@
         <v>3</v>
       </c>
       <c r="F125" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="G125">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H125" t="s">
         <v>25</v>
@@ -5234,7 +5257,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B126" t="s">
         <v>201</v>
@@ -5249,10 +5272,10 @@
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="G126">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H126" t="s">
         <v>25</v>
@@ -5260,7 +5283,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B127" t="s">
         <v>201</v>
@@ -5275,10 +5298,10 @@
         <v>3</v>
       </c>
       <c r="F127" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G127">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H127" t="s">
         <v>25</v>
@@ -5286,7 +5309,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B128" t="s">
         <v>201</v>
@@ -5301,10 +5324,10 @@
         <v>3</v>
       </c>
       <c r="F128" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="G128">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H128" t="s">
         <v>25</v>
@@ -5312,7 +5335,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B129" t="s">
         <v>201</v>
@@ -5327,10 +5350,10 @@
         <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="G129">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H129" t="s">
         <v>25</v>
@@ -5338,7 +5361,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B130" t="s">
         <v>201</v>
@@ -5353,10 +5376,10 @@
         <v>3</v>
       </c>
       <c r="F130" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="G130">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H130" t="s">
         <v>25</v>
@@ -5364,7 +5387,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B131" t="s">
         <v>201</v>
@@ -5379,10 +5402,10 @@
         <v>3</v>
       </c>
       <c r="F131" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G131">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H131" t="s">
         <v>25</v>
@@ -5390,7 +5413,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B132" t="s">
         <v>201</v>
@@ -5405,10 +5428,10 @@
         <v>3</v>
       </c>
       <c r="F132" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="G132">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H132" t="s">
         <v>25</v>
@@ -5416,7 +5439,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B133" t="s">
         <v>201</v>
@@ -5431,10 +5454,10 @@
         <v>3</v>
       </c>
       <c r="F133" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="G133">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H133" t="s">
         <v>25</v>
@@ -5442,7 +5465,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B134" t="s">
         <v>201</v>
@@ -5457,10 +5480,10 @@
         <v>3</v>
       </c>
       <c r="F134" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="G134">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H134" t="s">
         <v>25</v>
@@ -5468,7 +5491,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B135" t="s">
         <v>201</v>
@@ -5483,10 +5506,10 @@
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G135">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H135" t="s">
         <v>25</v>
@@ -5494,7 +5517,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B136" t="s">
         <v>201</v>
@@ -5509,10 +5532,10 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="G136">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H136" t="s">
         <v>25</v>
@@ -5520,7 +5543,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B137" t="s">
         <v>201</v>
@@ -5535,10 +5558,10 @@
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="G137">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H137" t="s">
         <v>25</v>
@@ -5546,7 +5569,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B138" t="s">
         <v>201</v>
@@ -5561,10 +5584,10 @@
         <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G138">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H138" t="s">
         <v>25</v>
@@ -5572,7 +5595,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B139" t="s">
         <v>201</v>
@@ -5587,10 +5610,10 @@
         <v>3</v>
       </c>
       <c r="F139" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="G139">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H139" t="s">
         <v>25</v>
@@ -5598,7 +5621,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B140" t="s">
         <v>201</v>
@@ -5613,10 +5636,10 @@
         <v>3</v>
       </c>
       <c r="F140" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="G140">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H140" t="s">
         <v>25</v>
@@ -5624,7 +5647,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B141" t="s">
         <v>201</v>
@@ -5639,10 +5662,10 @@
         <v>3</v>
       </c>
       <c r="F141" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="G141">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H141" t="s">
         <v>25</v>
@@ -5650,7 +5673,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B142" t="s">
         <v>201</v>
@@ -5665,10 +5688,10 @@
         <v>3</v>
       </c>
       <c r="F142" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="G142">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H142" t="s">
         <v>25</v>
@@ -5676,7 +5699,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B143" t="s">
         <v>201</v>
@@ -5691,10 +5714,10 @@
         <v>3</v>
       </c>
       <c r="F143" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="G143">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H143" t="s">
         <v>25</v>
@@ -5702,7 +5725,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B144" t="s">
         <v>201</v>
@@ -5717,10 +5740,10 @@
         <v>3</v>
       </c>
       <c r="F144" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G144">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H144" t="s">
         <v>25</v>
@@ -5728,7 +5751,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B145" t="s">
         <v>201</v>
@@ -5743,10 +5766,10 @@
         <v>3</v>
       </c>
       <c r="F145" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="G145">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H145" t="s">
         <v>25</v>
@@ -5754,7 +5777,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B146" t="s">
         <v>201</v>
@@ -5769,10 +5792,10 @@
         <v>3</v>
       </c>
       <c r="F146" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="G146">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H146" t="s">
         <v>25</v>
@@ -5780,7 +5803,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B147" t="s">
         <v>201</v>
@@ -5795,10 +5818,10 @@
         <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G147">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H147" t="s">
         <v>25</v>
@@ -5806,7 +5829,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B148" t="s">
         <v>201</v>
@@ -5821,10 +5844,10 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G148">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H148" t="s">
         <v>25</v>
@@ -5832,7 +5855,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B149" t="s">
         <v>201</v>
@@ -5847,10 +5870,10 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="G149">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H149" t="s">
         <v>25</v>
@@ -5858,7 +5881,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B150" t="s">
         <v>201</v>
@@ -5873,10 +5896,10 @@
         <v>3</v>
       </c>
       <c r="F150" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G150">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H150" t="s">
         <v>25</v>
@@ -5884,7 +5907,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B151" t="s">
         <v>201</v>
@@ -5899,10 +5922,10 @@
         <v>3</v>
       </c>
       <c r="F151" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="G151">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H151" t="s">
         <v>25</v>
@@ -5910,7 +5933,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B152" t="s">
         <v>201</v>
@@ -5925,10 +5948,10 @@
         <v>3</v>
       </c>
       <c r="F152" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G152">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H152" t="s">
         <v>25</v>
@@ -5936,7 +5959,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B153" t="s">
         <v>201</v>
@@ -5951,10 +5974,10 @@
         <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="G153">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H153" t="s">
         <v>25</v>
@@ -5962,7 +5985,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B154" t="s">
         <v>201</v>
@@ -5977,10 +6000,10 @@
         <v>3</v>
       </c>
       <c r="F154" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="G154">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H154" t="s">
         <v>25</v>
@@ -5988,7 +6011,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B155" t="s">
         <v>201</v>
@@ -6003,10 +6026,10 @@
         <v>3</v>
       </c>
       <c r="F155" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="G155">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H155" t="s">
         <v>25</v>
@@ -6014,7 +6037,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B156" t="s">
         <v>201</v>
@@ -6029,10 +6052,10 @@
         <v>3</v>
       </c>
       <c r="F156" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="G156">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H156" t="s">
         <v>25</v>
@@ -6040,7 +6063,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B157" t="s">
         <v>201</v>
@@ -6055,10 +6078,10 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G157">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H157" t="s">
         <v>25</v>
@@ -6066,7 +6089,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B158" t="s">
         <v>201</v>
@@ -6081,10 +6104,10 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G158">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H158" t="s">
         <v>25</v>
@@ -6092,7 +6115,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B159" t="s">
         <v>201</v>
@@ -6107,10 +6130,10 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="G159">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H159" t="s">
         <v>25</v>
@@ -6118,7 +6141,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B160" t="s">
         <v>201</v>
@@ -6133,10 +6156,10 @@
         <v>3</v>
       </c>
       <c r="F160" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="G160">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H160" t="s">
         <v>25</v>
@@ -6144,7 +6167,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B161" t="s">
         <v>201</v>
@@ -6159,10 +6182,10 @@
         <v>3</v>
       </c>
       <c r="F161" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="G161">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H161" t="s">
         <v>25</v>
@@ -6170,7 +6193,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B162" t="s">
         <v>201</v>
@@ -6185,10 +6208,10 @@
         <v>3</v>
       </c>
       <c r="F162" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="G162">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H162" t="s">
         <v>25</v>
@@ -6196,7 +6219,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B163" t="s">
         <v>201</v>
@@ -6211,10 +6234,10 @@
         <v>3</v>
       </c>
       <c r="F163" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G163">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H163" t="s">
         <v>25</v>
@@ -6222,7 +6245,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B164" t="s">
         <v>201</v>
@@ -6237,10 +6260,10 @@
         <v>3</v>
       </c>
       <c r="F164" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="G164">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H164" t="s">
         <v>25</v>
@@ -6248,7 +6271,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B165" t="s">
         <v>201</v>
@@ -6263,10 +6286,10 @@
         <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="G165">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H165" t="s">
         <v>25</v>
@@ -6274,7 +6297,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B166" t="s">
         <v>201</v>
@@ -6289,10 +6312,10 @@
         <v>3</v>
       </c>
       <c r="F166" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="G166">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H166" t="s">
         <v>25</v>
@@ -6300,7 +6323,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B167" t="s">
         <v>201</v>
@@ -6315,10 +6338,10 @@
         <v>3</v>
       </c>
       <c r="F167" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G167">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H167" t="s">
         <v>25</v>
@@ -6326,7 +6349,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B168" t="s">
         <v>201</v>
@@ -6341,10 +6364,10 @@
         <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G168">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H168" t="s">
         <v>25</v>
@@ -6352,7 +6375,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B169" t="s">
         <v>201</v>
@@ -6367,10 +6390,10 @@
         <v>3</v>
       </c>
       <c r="F169" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="G169">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H169" t="s">
         <v>25</v>
@@ -6378,7 +6401,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B170" t="s">
         <v>201</v>
@@ -6393,10 +6416,10 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="G170">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H170" t="s">
         <v>25</v>
@@ -6404,7 +6427,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B171" t="s">
         <v>201</v>
@@ -6419,10 +6442,10 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="G171">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H171" t="s">
         <v>25</v>
@@ -6430,7 +6453,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B172" t="s">
         <v>201</v>
@@ -6445,10 +6468,10 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="G172">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H172" t="s">
         <v>25</v>
@@ -6456,7 +6479,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B173" t="s">
         <v>201</v>
@@ -6471,10 +6494,10 @@
         <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G173">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H173" t="s">
         <v>25</v>
@@ -6482,7 +6505,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B174" t="s">
         <v>201</v>
@@ -6497,10 +6520,10 @@
         <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="G174">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H174" t="s">
         <v>25</v>
@@ -6508,7 +6531,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B175" t="s">
         <v>201</v>
@@ -6523,10 +6546,10 @@
         <v>3</v>
       </c>
       <c r="F175" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="G175">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H175" t="s">
         <v>25</v>
@@ -6534,51 +6557,51 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B176" t="s">
-        <v>371</v>
+        <v>201</v>
       </c>
       <c r="C176" t="s">
-        <v>372</v>
+        <v>202</v>
       </c>
       <c r="D176" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F176" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="H176" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B177" t="s">
-        <v>374</v>
+        <v>201</v>
       </c>
       <c r="C177" t="s">
-        <v>375</v>
+        <v>202</v>
       </c>
       <c r="D177" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="G177">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="H177" t="s">
         <v>25</v>
@@ -6586,25 +6609,25 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="B178" t="s">
-        <v>374</v>
+        <v>201</v>
       </c>
       <c r="C178" t="s">
-        <v>375</v>
+        <v>202</v>
       </c>
       <c r="D178" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E178">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="G178">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H178" t="s">
         <v>25</v>
@@ -6612,33 +6635,33 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B179" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C179" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D179" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="G179">
         <v>1</v>
       </c>
       <c r="H179" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="B180" t="s">
         <v>374</v>
@@ -6647,16 +6670,16 @@
         <v>375</v>
       </c>
       <c r="D180" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="G180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180" t="s">
         <v>25</v>
@@ -6664,7 +6687,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B181" t="s">
         <v>374</v>
@@ -6673,16 +6696,16 @@
         <v>375</v>
       </c>
       <c r="D181" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="G181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H181" t="s">
         <v>25</v>
@@ -6690,7 +6713,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B182" t="s">
         <v>374</v>
@@ -6705,10 +6728,10 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="G182">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H182" t="s">
         <v>25</v>
@@ -6716,7 +6739,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B183" t="s">
         <v>374</v>
@@ -6731,10 +6754,10 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H183" t="s">
         <v>25</v>
@@ -6742,7 +6765,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B184" t="s">
         <v>374</v>
@@ -6757,10 +6780,10 @@
         <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="G184">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H184" t="s">
         <v>25</v>
@@ -6768,7 +6791,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B185" t="s">
         <v>374</v>
@@ -6783,10 +6806,10 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="G185">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H185" t="s">
         <v>25</v>
@@ -6794,7 +6817,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B186" t="s">
         <v>374</v>
@@ -6809,10 +6832,10 @@
         <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="G186">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H186" t="s">
         <v>25</v>
@@ -6820,7 +6843,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B187" t="s">
         <v>374</v>
@@ -6835,10 +6858,10 @@
         <v>3</v>
       </c>
       <c r="F187" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G187">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H187" t="s">
         <v>25</v>
@@ -6846,7 +6869,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B188" t="s">
         <v>374</v>
@@ -6861,10 +6884,10 @@
         <v>3</v>
       </c>
       <c r="F188" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="G188">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H188" t="s">
         <v>25</v>
@@ -6872,7 +6895,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B189" t="s">
         <v>374</v>
@@ -6887,10 +6910,10 @@
         <v>3</v>
       </c>
       <c r="F189" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G189">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H189" t="s">
         <v>25</v>
@@ -6898,7 +6921,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B190" t="s">
         <v>374</v>
@@ -6913,10 +6936,10 @@
         <v>3</v>
       </c>
       <c r="F190" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="G190">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H190" t="s">
         <v>25</v>
@@ -6924,7 +6947,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B191" t="s">
         <v>374</v>
@@ -6939,10 +6962,10 @@
         <v>3</v>
       </c>
       <c r="F191" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="G191">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H191" t="s">
         <v>25</v>
@@ -6950,7 +6973,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B192" t="s">
         <v>374</v>
@@ -6965,10 +6988,10 @@
         <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="G192">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H192" t="s">
         <v>25</v>
@@ -6976,7 +6999,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B193" t="s">
         <v>374</v>
@@ -6991,10 +7014,10 @@
         <v>3</v>
       </c>
       <c r="F193" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="G193">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H193" t="s">
         <v>25</v>
@@ -7002,7 +7025,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B194" t="s">
         <v>374</v>
@@ -7017,10 +7040,10 @@
         <v>3</v>
       </c>
       <c r="F194" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="G194">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H194" t="s">
         <v>25</v>
@@ -7028,7 +7051,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B195" t="s">
         <v>374</v>
@@ -7043,10 +7066,10 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="G195">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H195" t="s">
         <v>25</v>
@@ -7054,7 +7077,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="B196" t="s">
         <v>374</v>
@@ -7069,10 +7092,10 @@
         <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G196">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H196" t="s">
         <v>25</v>
@@ -7080,7 +7103,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B197" t="s">
         <v>374</v>
@@ -7095,10 +7118,10 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="G197">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H197" t="s">
         <v>25</v>
@@ -7106,7 +7129,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B198" t="s">
         <v>374</v>
@@ -7121,10 +7144,10 @@
         <v>3</v>
       </c>
       <c r="F198" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="G198">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H198" t="s">
         <v>25</v>
@@ -7132,7 +7155,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B199" t="s">
         <v>374</v>
@@ -7147,10 +7170,10 @@
         <v>3</v>
       </c>
       <c r="F199" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G199">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H199" t="s">
         <v>25</v>
@@ -7158,7 +7181,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B200" t="s">
         <v>374</v>
@@ -7173,10 +7196,10 @@
         <v>3</v>
       </c>
       <c r="F200" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G200">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H200" t="s">
         <v>25</v>
@@ -7184,7 +7207,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B201" t="s">
         <v>374</v>
@@ -7199,10 +7222,10 @@
         <v>3</v>
       </c>
       <c r="F201" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G201">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H201" t="s">
         <v>25</v>
@@ -7210,7 +7233,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B202" t="s">
         <v>374</v>
@@ -7225,10 +7248,10 @@
         <v>3</v>
       </c>
       <c r="F202" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G202">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H202" t="s">
         <v>25</v>
@@ -7236,7 +7259,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="B203" t="s">
         <v>374</v>
@@ -7251,10 +7274,10 @@
         <v>3</v>
       </c>
       <c r="F203" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G203">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H203" t="s">
         <v>25</v>
@@ -7262,7 +7285,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B204" t="s">
         <v>374</v>
@@ -7277,10 +7300,10 @@
         <v>3</v>
       </c>
       <c r="F204" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="G204">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H204" t="s">
         <v>25</v>
@@ -7288,25 +7311,25 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="B205" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="C205" t="s">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="D205" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E205">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F205" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="G205">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H205" t="s">
         <v>25</v>
@@ -7314,25 +7337,25 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="B206" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="C206" t="s">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="D206" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F206" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="G206">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H206" t="s">
         <v>25</v>
@@ -7340,25 +7363,25 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B207" t="s">
-        <v>431</v>
+        <v>374</v>
       </c>
       <c r="C207" t="s">
-        <v>432</v>
+        <v>375</v>
       </c>
       <c r="D207" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F207" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G207">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H207" t="s">
         <v>25</v>
@@ -7366,7 +7389,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="B208" t="s">
         <v>431</v>
@@ -7375,13 +7398,13 @@
         <v>432</v>
       </c>
       <c r="D208" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F208" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="G208">
         <v>1</v>
@@ -7392,7 +7415,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B209" t="s">
         <v>431</v>
@@ -7401,13 +7424,13 @@
         <v>432</v>
       </c>
       <c r="D209" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F209" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="G209">
         <v>2</v>
@@ -7418,7 +7441,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B210" t="s">
         <v>431</v>
@@ -7427,13 +7450,13 @@
         <v>432</v>
       </c>
       <c r="D210" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E210">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F210" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G210">
         <v>3</v>
@@ -7444,7 +7467,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B211" t="s">
         <v>431</v>
@@ -7459,10 +7482,10 @@
         <v>3</v>
       </c>
       <c r="F211" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="G211">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H211" t="s">
         <v>25</v>
@@ -7470,7 +7493,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B212" t="s">
         <v>431</v>
@@ -7485,10 +7508,10 @@
         <v>3</v>
       </c>
       <c r="F212" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="G212">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H212" t="s">
         <v>25</v>
@@ -7496,7 +7519,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="B213" t="s">
         <v>431</v>
@@ -7511,10 +7534,10 @@
         <v>3</v>
       </c>
       <c r="F213" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G213">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H213" t="s">
         <v>25</v>
@@ -7522,7 +7545,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="B214" t="s">
         <v>431</v>
@@ -7537,10 +7560,10 @@
         <v>3</v>
       </c>
       <c r="F214" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="G214">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H214" t="s">
         <v>25</v>
@@ -7548,7 +7571,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B215" t="s">
         <v>431</v>
@@ -7563,10 +7586,10 @@
         <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="G215">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H215" t="s">
         <v>25</v>
@@ -7574,7 +7597,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B216" t="s">
         <v>431</v>
@@ -7589,10 +7612,10 @@
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="G216">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H216" t="s">
         <v>25</v>
@@ -7600,7 +7623,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="B217" t="s">
         <v>431</v>
@@ -7615,10 +7638,10 @@
         <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="G217">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H217" t="s">
         <v>25</v>
@@ -7626,7 +7649,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B218" t="s">
         <v>431</v>
@@ -7641,10 +7664,10 @@
         <v>3</v>
       </c>
       <c r="F218" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="G218">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H218" t="s">
         <v>25</v>
@@ -7652,7 +7675,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B219" t="s">
         <v>431</v>
@@ -7667,10 +7690,10 @@
         <v>3</v>
       </c>
       <c r="F219" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G219">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H219" t="s">
         <v>25</v>
@@ -7678,7 +7701,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="B220" t="s">
         <v>431</v>
@@ -7693,10 +7716,10 @@
         <v>3</v>
       </c>
       <c r="F220" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="G220">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H220" t="s">
         <v>25</v>
@@ -7704,7 +7727,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="B221" t="s">
         <v>431</v>
@@ -7719,10 +7742,10 @@
         <v>3</v>
       </c>
       <c r="F221" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="G221">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H221" t="s">
         <v>25</v>
@@ -7730,7 +7753,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B222" t="s">
         <v>431</v>
@@ -7745,10 +7768,10 @@
         <v>3</v>
       </c>
       <c r="F222" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="G222">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H222" t="s">
         <v>25</v>
@@ -7756,7 +7779,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B223" t="s">
         <v>431</v>
@@ -7771,10 +7794,10 @@
         <v>3</v>
       </c>
       <c r="F223" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="G223">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H223" t="s">
         <v>25</v>
@@ -7782,7 +7805,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B224" t="s">
         <v>431</v>
@@ -7797,10 +7820,10 @@
         <v>3</v>
       </c>
       <c r="F224" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="G224">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H224" t="s">
         <v>25</v>
@@ -7808,7 +7831,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B225" t="s">
         <v>431</v>
@@ -7823,10 +7846,10 @@
         <v>3</v>
       </c>
       <c r="F225" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="G225">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H225" t="s">
         <v>25</v>
@@ -7834,7 +7857,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="B226" t="s">
         <v>431</v>
@@ -7849,10 +7872,10 @@
         <v>3</v>
       </c>
       <c r="F226" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="G226">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H226" t="s">
         <v>25</v>
@@ -7860,7 +7883,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="B227" t="s">
         <v>431</v>
@@ -7875,10 +7898,10 @@
         <v>3</v>
       </c>
       <c r="F227" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="G227">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H227" t="s">
         <v>25</v>
@@ -7886,7 +7909,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B228" t="s">
         <v>431</v>
@@ -7901,10 +7924,10 @@
         <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="G228">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H228" t="s">
         <v>25</v>
@@ -7912,7 +7935,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B229" t="s">
         <v>431</v>
@@ -7927,10 +7950,10 @@
         <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="G229">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H229" t="s">
         <v>25</v>
@@ -7938,7 +7961,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B230" t="s">
         <v>431</v>
@@ -7953,10 +7976,10 @@
         <v>3</v>
       </c>
       <c r="F230" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="G230">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H230" t="s">
         <v>25</v>
@@ -7964,7 +7987,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B231" t="s">
         <v>431</v>
@@ -7979,10 +8002,10 @@
         <v>3</v>
       </c>
       <c r="F231" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="G231">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H231" t="s">
         <v>25</v>
@@ -7990,7 +8013,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B232" t="s">
         <v>431</v>
@@ -8005,10 +8028,10 @@
         <v>3</v>
       </c>
       <c r="F232" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G232">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H232" t="s">
         <v>25</v>
@@ -8016,7 +8039,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B233" t="s">
         <v>431</v>
@@ -8031,10 +8054,10 @@
         <v>3</v>
       </c>
       <c r="F233" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="G233">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H233" t="s">
         <v>25</v>
@@ -8042,7 +8065,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="B234" t="s">
         <v>431</v>
@@ -8057,10 +8080,10 @@
         <v>3</v>
       </c>
       <c r="F234" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="G234">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H234" t="s">
         <v>25</v>
@@ -8068,7 +8091,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B235" t="s">
         <v>431</v>
@@ -8083,10 +8106,10 @@
         <v>3</v>
       </c>
       <c r="F235" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G235">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H235" t="s">
         <v>25</v>
@@ -8094,7 +8117,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B236" t="s">
         <v>431</v>
@@ -8109,10 +8132,10 @@
         <v>3</v>
       </c>
       <c r="F236" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G236">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H236" t="s">
         <v>25</v>
@@ -8120,7 +8143,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B237" t="s">
         <v>431</v>
@@ -8135,10 +8158,10 @@
         <v>3</v>
       </c>
       <c r="F237" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="G237">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H237" t="s">
         <v>25</v>
@@ -8146,7 +8169,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B238" t="s">
         <v>431</v>
@@ -8161,10 +8184,10 @@
         <v>3</v>
       </c>
       <c r="F238" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="G238">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H238" t="s">
         <v>25</v>
@@ -8172,7 +8195,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B239" t="s">
         <v>431</v>
@@ -8187,10 +8210,10 @@
         <v>3</v>
       </c>
       <c r="F239" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="G239">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H239" t="s">
         <v>25</v>
@@ -8198,7 +8221,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B240" t="s">
         <v>431</v>
@@ -8213,10 +8236,10 @@
         <v>3</v>
       </c>
       <c r="F240" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="G240">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H240" t="s">
         <v>25</v>
@@ -8224,7 +8247,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B241" t="s">
         <v>431</v>
@@ -8239,10 +8262,10 @@
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="G241">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H241" t="s">
         <v>25</v>
@@ -8250,7 +8273,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="B242" t="s">
         <v>431</v>
@@ -8265,10 +8288,10 @@
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="G242">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H242" t="s">
         <v>25</v>
@@ -8276,7 +8299,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="B243" t="s">
         <v>431</v>
@@ -8291,10 +8314,10 @@
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="G243">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H243" t="s">
         <v>25</v>
@@ -8302,7 +8325,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B244" t="s">
         <v>431</v>
@@ -8317,10 +8340,10 @@
         <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="G244">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H244" t="s">
         <v>25</v>
@@ -8328,7 +8351,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B245" t="s">
         <v>431</v>
@@ -8343,10 +8366,10 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="G245">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H245" t="s">
         <v>25</v>
@@ -8354,7 +8377,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B246" t="s">
         <v>431</v>
@@ -8369,10 +8392,10 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="G246">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H246" t="s">
         <v>25</v>
@@ -8380,7 +8403,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B247" t="s">
         <v>431</v>
@@ -8395,10 +8418,10 @@
         <v>3</v>
       </c>
       <c r="F247" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="G247">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H247" t="s">
         <v>25</v>
@@ -8406,7 +8429,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B248" t="s">
         <v>431</v>
@@ -8421,12 +8444,90 @@
         <v>3</v>
       </c>
       <c r="F248" t="s">
+        <v>513</v>
+      </c>
+      <c r="G248">
+        <v>38</v>
+      </c>
+      <c r="H248" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>514</v>
+      </c>
+      <c r="B249" t="s">
+        <v>431</v>
+      </c>
+      <c r="C249" t="s">
+        <v>432</v>
+      </c>
+      <c r="D249" t="s">
+        <v>23</v>
+      </c>
+      <c r="E249">
+        <v>3</v>
+      </c>
+      <c r="F249" t="s">
+        <v>515</v>
+      </c>
+      <c r="G249">
+        <v>39</v>
+      </c>
+      <c r="H249" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>516</v>
+      </c>
+      <c r="B250" t="s">
+        <v>431</v>
+      </c>
+      <c r="C250" t="s">
+        <v>432</v>
+      </c>
+      <c r="D250" t="s">
+        <v>23</v>
+      </c>
+      <c r="E250">
+        <v>3</v>
+      </c>
+      <c r="F250" t="s">
+        <v>517</v>
+      </c>
+      <c r="G250">
+        <v>40</v>
+      </c>
+      <c r="H250" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>518</v>
+      </c>
+      <c r="B251" t="s">
+        <v>431</v>
+      </c>
+      <c r="C251" t="s">
+        <v>432</v>
+      </c>
+      <c r="D251" t="s">
+        <v>23</v>
+      </c>
+      <c r="E251">
+        <v>3</v>
+      </c>
+      <c r="F251" t="s">
         <v>519</v>
       </c>
-      <c r="G248">
+      <c r="G251">
         <v>41</v>
       </c>
-      <c r="H248" t="s">
+      <c r="H251" t="s">
         <v>25</v>
       </c>
     </row>
